--- a/outputs/560-12.xlsx
+++ b/outputs/560-12.xlsx
@@ -147,15 +147,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -428,6 +428,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="3" t="n">
+        <f aca="false">COUNTIF(B:B,I4)</f>
         <v>3</v>
       </c>
     </row>
@@ -448,6 +449,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="3" t="n">
+        <f aca="false">COUNTIF(B:B,I5)</f>
         <v>3</v>
       </c>
     </row>
@@ -468,6 +470,7 @@
         <v>9</v>
       </c>
       <c r="J6" s="3" t="n">
+        <f aca="false">COUNTIF(B:B,I6)</f>
         <v>3</v>
       </c>
     </row>

--- a/outputs/560-12.xlsx
+++ b/outputs/560-12.xlsx
@@ -40,13 +40,13 @@
     <t xml:space="preserve">Paper</t>
   </si>
   <si>
+    <t xml:space="preserve">Qty</t>
+  </si>
+  <si>
     <t xml:space="preserve">A004</t>
   </si>
   <si>
     <t xml:space="preserve">Pen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
   </si>
   <si>
     <t xml:space="preserve">A005</t>
@@ -142,7 +142,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -153,10 +153,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -375,7 +371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>123345</v>
       </c>
@@ -388,30 +384,34 @@
       <c r="D2" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>123345</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>123345</v>
       </c>
@@ -424,15 +424,14 @@
       <c r="D4" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <f aca="false">COUNTIF(B:B,I4)</f>
+      <c r="I4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>123346</v>
       </c>
@@ -445,36 +444,28 @@
       <c r="D5" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <f aca="false">COUNTIF(B:B,I5)</f>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>123346</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <f aca="false">COUNTIF(B:B,I6)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>123346</v>
       </c>
@@ -487,8 +478,6 @@
       <c r="D7" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
@@ -509,10 +498,10 @@
         <v>123347</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>100</v>
